--- a/sensitivity_weight_comparison.xlsx
+++ b/sensitivity_weight_comparison.xlsx
@@ -86442,7 +86442,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Energy intensity level of primary energy (MJ/$2017 PPP GDP)_x</t>
+          <t>Energy intensity level of primary energy (MJ/$2021 PPP GDP)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
